--- a/test_data/PHC-A_PAST.xlsx
+++ b/test_data/PHC-A_PAST.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="144">
   <si>
     <t>Registration Date</t>
   </si>
@@ -67,6 +67,12 @@
     <t>Blood Sugar Value</t>
   </si>
   <si>
+    <t>Diagnosis 1</t>
+  </si>
+  <si>
+    <t>Diagnosis 2</t>
+  </si>
+  <si>
     <t>29-01-2026 00:00:00</t>
   </si>
   <si>
@@ -295,126 +301,6 @@
     <t>Patient</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>01-01-1980</t>
   </si>
   <si>
@@ -487,70 +373,79 @@
     <t>SHC-C</t>
   </si>
   <si>
-    <t>27-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>28-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>25-12-2025 00:00:00</t>
+    <t>25-05-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>27-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>28-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>25-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>17-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>26-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>17-03-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>25-11-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>21-03-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>03-03-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>17-04-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>01-05-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>24-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>15-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>13-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>06-05-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>03-05-2026 00:00:00</t>
   </si>
   <si>
     <t>17-12-2025 00:00:00</t>
   </si>
   <si>
-    <t>26-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>17-11-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>25-07-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>21-11-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>03-11-2024 00:00:00</t>
-  </si>
-  <si>
-    <t>17-12-2024 00:00:00</t>
-  </si>
-  <si>
-    <t>01-01-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>24-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>15-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>13-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>06-01-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>03-01-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>19-01-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>30-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>17-09-2024 00:00:00</t>
-  </si>
-  <si>
-    <t>07-01-2025 00:00:00</t>
+    <t>19-05-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>30-04-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>17-01-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>07-05-2025 00:00:00</t>
   </si>
   <si>
     <t>FBS</t>
+  </si>
+  <si>
+    <t>I10</t>
+  </si>
+  <si>
+    <t>E11</t>
   </si>
 </sst>
 </file>
@@ -908,10 +803,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -963,37 +858,43 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="G2" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H2">
         <v>1640879532</v>
       </c>
       <c r="J2" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K2" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L2" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M2">
         <v>133</v>
@@ -1001,40 +902,40 @@
       <c r="N2">
         <v>84</v>
       </c>
-      <c r="P2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>94</v>
+        <v>94</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H3">
         <v>9001641291</v>
       </c>
       <c r="J3" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K3" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M3">
         <v>131</v>
@@ -1042,40 +943,40 @@
       <c r="N3">
         <v>83</v>
       </c>
-      <c r="P3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H4">
         <v>9004736657</v>
       </c>
       <c r="J4" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K4" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L4" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M4">
         <v>120</v>
@@ -1084,45 +985,51 @@
         <v>80</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q4">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>142</v>
+      </c>
+      <c r="S4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" t="s">
-        <v>96</v>
+        <v>94</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H5">
         <v>5037957603</v>
       </c>
       <c r="J5" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K5" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L5" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M5">
         <v>120</v>
@@ -1131,45 +1038,51 @@
         <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="P5" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q5">
         <v>120</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" t="s">
+        <v>142</v>
+      </c>
+      <c r="S5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="G6" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H6">
         <v>7450089069</v>
       </c>
       <c r="J6" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K6" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M6">
         <v>120</v>
@@ -1178,45 +1091,51 @@
         <v>80</v>
       </c>
       <c r="O6" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="P6" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q6">
         <v>120</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6" t="s">
+        <v>142</v>
+      </c>
+      <c r="S6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H7">
         <v>5642953020</v>
       </c>
       <c r="J7" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K7" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M7">
         <v>120</v>
@@ -1225,45 +1144,51 @@
         <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="P7" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q7">
         <v>120</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" t="s">
+        <v>142</v>
+      </c>
+      <c r="S7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H8">
         <v>3767920156</v>
       </c>
       <c r="J8" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K8" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L8" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M8">
         <v>120</v>
@@ -1272,45 +1197,51 @@
         <v>80</v>
       </c>
       <c r="O8" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q8">
         <v>120</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8" t="s">
+        <v>142</v>
+      </c>
+      <c r="S8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="G9" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H9">
         <v>2391944891</v>
       </c>
       <c r="J9" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K9" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L9" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="M9">
         <v>120</v>
@@ -1319,42 +1250,48 @@
         <v>80</v>
       </c>
       <c r="O9" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="P9" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q9">
         <v>120</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9" t="s">
+        <v>142</v>
+      </c>
+      <c r="S9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K10" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L10" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="M10">
         <v>141</v>
@@ -1363,45 +1300,51 @@
         <v>91</v>
       </c>
       <c r="O10" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q10">
         <v>130</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>102</v>
       </c>
-      <c r="F11" t="s">
-        <v>140</v>
-      </c>
       <c r="G11" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H11">
         <v>3420998771</v>
       </c>
       <c r="J11" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K11" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M11">
         <v>115</v>
@@ -1410,39 +1353,39 @@
         <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>163</v>
-      </c>
-      <c r="P11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>126</v>
+      </c>
+      <c r="R11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
         <v>103</v>
       </c>
-      <c r="F12" t="s">
-        <v>141</v>
-      </c>
       <c r="G12" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K12" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M12">
         <v>141</v>
@@ -1451,45 +1394,51 @@
         <v>91</v>
       </c>
       <c r="O12" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q12">
         <v>130</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" t="s">
+        <v>142</v>
+      </c>
+      <c r="S12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
         <v>104</v>
       </c>
-      <c r="F13" t="s">
-        <v>142</v>
-      </c>
       <c r="G13" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H13">
         <v>4015464640</v>
       </c>
       <c r="J13" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M13">
         <v>132</v>
@@ -1498,42 +1447,42 @@
         <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>165</v>
-      </c>
-      <c r="P13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
+        <v>128</v>
+      </c>
+      <c r="R13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
         <v>105</v>
       </c>
-      <c r="F14" t="s">
-        <v>143</v>
-      </c>
       <c r="G14" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H14">
         <v>2515858745</v>
       </c>
       <c r="J14" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K14" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="M14">
         <v>127</v>
@@ -1542,42 +1491,42 @@
         <v>79</v>
       </c>
       <c r="O14" t="s">
-        <v>166</v>
-      </c>
-      <c r="P14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>129</v>
+      </c>
+      <c r="R14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
         <v>106</v>
       </c>
-      <c r="F15" t="s">
-        <v>144</v>
-      </c>
       <c r="G15" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H15">
         <v>2834539761</v>
       </c>
       <c r="J15" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L15" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="M15">
         <v>128</v>
@@ -1586,42 +1535,42 @@
         <v>85</v>
       </c>
       <c r="O15" t="s">
-        <v>167</v>
-      </c>
-      <c r="P15" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>130</v>
+      </c>
+      <c r="R15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>107</v>
+        <v>94</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="G16" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H16">
         <v>2519605117</v>
       </c>
       <c r="J16" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K16" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L16" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M16">
         <v>120</v>
@@ -1629,37 +1578,37 @@
       <c r="N16">
         <v>75</v>
       </c>
-      <c r="P16" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="E17">
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K17" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M17">
         <v>132</v>
@@ -1667,37 +1616,37 @@
       <c r="N17">
         <v>82</v>
       </c>
-      <c r="P17" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" t="s">
-        <v>109</v>
+        <v>94</v>
+      </c>
+      <c r="E18">
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="G18" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="J18" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K18" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M18">
         <v>134</v>
@@ -1705,37 +1654,37 @@
       <c r="N18">
         <v>75</v>
       </c>
-      <c r="P18" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="E19" t="s">
-        <v>110</v>
+        <v>94</v>
+      </c>
+      <c r="E19">
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J19" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K19" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L19" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M19">
         <v>118</v>
@@ -1743,37 +1692,37 @@
       <c r="N19">
         <v>85</v>
       </c>
-      <c r="P19" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" t="s">
-        <v>111</v>
+        <v>94</v>
+      </c>
+      <c r="E20">
+        <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="G20" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J20" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K20" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L20" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M20">
         <v>122</v>
@@ -1781,40 +1730,40 @@
       <c r="N20">
         <v>75</v>
       </c>
-      <c r="P20" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" t="s">
-        <v>112</v>
+        <v>94</v>
+      </c>
+      <c r="E21">
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H21">
         <v>4291035954</v>
       </c>
       <c r="J21" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K21" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L21" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M21">
         <v>128</v>
@@ -1822,40 +1771,40 @@
       <c r="N21">
         <v>84</v>
       </c>
-      <c r="P21" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" t="s">
-        <v>113</v>
+        <v>94</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H22">
         <v>1640879532</v>
       </c>
       <c r="J22" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K22" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L22" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M22">
         <v>124</v>
@@ -1863,40 +1812,40 @@
       <c r="N22">
         <v>78</v>
       </c>
-      <c r="P22" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" t="s">
-        <v>114</v>
+        <v>94</v>
+      </c>
+      <c r="E23">
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H23">
         <v>9001641291</v>
       </c>
       <c r="J23" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K23" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L23" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M23">
         <v>131</v>
@@ -1904,40 +1853,40 @@
       <c r="N23">
         <v>80</v>
       </c>
-      <c r="P23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" t="s">
-        <v>115</v>
+        <v>94</v>
+      </c>
+      <c r="E24">
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H24">
         <v>3767920156</v>
       </c>
       <c r="J24" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K24" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L24" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M24">
         <v>120</v>
@@ -1946,45 +1895,51 @@
         <v>80</v>
       </c>
       <c r="O24" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="P24" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q24">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24" t="s">
+        <v>142</v>
+      </c>
+      <c r="S24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" t="s">
-        <v>116</v>
+        <v>94</v>
+      </c>
+      <c r="E25">
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="G25" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H25">
         <v>9004736657</v>
       </c>
       <c r="J25" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K25" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L25" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M25">
         <v>120</v>
@@ -1993,45 +1948,51 @@
         <v>80</v>
       </c>
       <c r="O25" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="P25" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q25">
         <v>120</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25" t="s">
+        <v>142</v>
+      </c>
+      <c r="S25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" t="s">
-        <v>117</v>
+        <v>94</v>
+      </c>
+      <c r="E26">
+        <v>26</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H26">
         <v>5037957603</v>
       </c>
       <c r="J26" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K26" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L26" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M26">
         <v>120</v>
@@ -2040,45 +2001,51 @@
         <v>80</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q26">
         <v>120</v>
       </c>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="R26" t="s">
+        <v>142</v>
+      </c>
+      <c r="S26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" t="s">
-        <v>118</v>
+        <v>94</v>
+      </c>
+      <c r="E27">
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H27">
         <v>7450089069</v>
       </c>
       <c r="J27" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K27" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L27" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M27">
         <v>120</v>
@@ -2087,45 +2054,51 @@
         <v>80</v>
       </c>
       <c r="O27" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q27">
         <v>120</v>
       </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="R27" t="s">
+        <v>142</v>
+      </c>
+      <c r="S27" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" t="s">
-        <v>119</v>
+        <v>94</v>
+      </c>
+      <c r="E28">
+        <v>28</v>
       </c>
       <c r="F28" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="G28" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H28">
         <v>5642953020</v>
       </c>
       <c r="J28" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K28" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M28">
         <v>120</v>
@@ -2134,45 +2107,51 @@
         <v>80</v>
       </c>
       <c r="O28" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q28">
         <v>120</v>
       </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="R28" t="s">
+        <v>142</v>
+      </c>
+      <c r="S28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" t="s">
-        <v>120</v>
+        <v>94</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
       </c>
       <c r="F29" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="G29" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H29">
         <v>2391944891</v>
       </c>
       <c r="J29" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K29" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="M29">
         <v>120</v>
@@ -2181,42 +2160,48 @@
         <v>80</v>
       </c>
       <c r="O29" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q29">
         <v>120</v>
       </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="R29" t="s">
+        <v>142</v>
+      </c>
+      <c r="S29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="E30">
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J30" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K30" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="M30">
         <v>128</v>
@@ -2225,42 +2210,42 @@
         <v>80</v>
       </c>
       <c r="O30" t="s">
-        <v>173</v>
-      </c>
-      <c r="P30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
+        <v>136</v>
+      </c>
+      <c r="R30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" t="s">
-        <v>122</v>
+        <v>94</v>
+      </c>
+      <c r="E31">
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="G31" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H31">
         <v>3420998771</v>
       </c>
       <c r="J31" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K31" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L31" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M31">
         <v>141</v>
@@ -2269,42 +2254,48 @@
         <v>91</v>
       </c>
       <c r="O31" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q31">
         <v>130</v>
       </c>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="R31" t="s">
+        <v>142</v>
+      </c>
+      <c r="S31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" t="s">
-        <v>123</v>
+        <v>94</v>
+      </c>
+      <c r="E32">
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="J32" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K32" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M32">
         <v>141</v>
@@ -2313,45 +2304,51 @@
         <v>91</v>
       </c>
       <c r="O32" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="Q32">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="R32" t="s">
+        <v>142</v>
+      </c>
+      <c r="S32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" t="s">
-        <v>124</v>
+        <v>94</v>
+      </c>
+      <c r="E33">
+        <v>34</v>
       </c>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H33">
         <v>4015464640</v>
       </c>
       <c r="J33" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K33" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="M33">
         <v>127</v>
@@ -2360,42 +2357,42 @@
         <v>77</v>
       </c>
       <c r="O33" t="s">
-        <v>165</v>
-      </c>
-      <c r="P33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+        <v>128</v>
+      </c>
+      <c r="R33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
-      </c>
-      <c r="E34" t="s">
-        <v>125</v>
+        <v>94</v>
+      </c>
+      <c r="E34">
+        <v>35</v>
       </c>
       <c r="F34" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H34">
         <v>2515858745</v>
       </c>
       <c r="J34" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K34" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L34" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="M34">
         <v>123</v>
@@ -2404,42 +2401,42 @@
         <v>79</v>
       </c>
       <c r="O34" t="s">
-        <v>176</v>
-      </c>
-      <c r="P34" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+        <v>139</v>
+      </c>
+      <c r="R34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" t="s">
-        <v>126</v>
+        <v>94</v>
+      </c>
+      <c r="E35">
+        <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="G35" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H35">
         <v>2834539761</v>
       </c>
       <c r="J35" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K35" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L35" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="M35">
         <v>119</v>
@@ -2448,42 +2445,42 @@
         <v>76</v>
       </c>
       <c r="O35" t="s">
-        <v>177</v>
-      </c>
-      <c r="P35" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
+        <v>140</v>
+      </c>
+      <c r="R35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" t="s">
-        <v>127</v>
+        <v>94</v>
+      </c>
+      <c r="E36">
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="G36" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="H36">
         <v>2519605117</v>
       </c>
       <c r="J36" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K36" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M36">
         <v>115</v>
@@ -2491,37 +2488,37 @@
       <c r="N36">
         <v>75</v>
       </c>
-      <c r="P36" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="R36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E37" t="s">
-        <v>128</v>
+        <v>94</v>
+      </c>
+      <c r="E37">
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="G37" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J37" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K37" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M37">
         <v>120</v>
@@ -2529,37 +2526,37 @@
       <c r="N37">
         <v>85</v>
       </c>
-      <c r="P37" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="R37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E38" t="s">
-        <v>129</v>
+        <v>94</v>
+      </c>
+      <c r="E38">
+        <v>39</v>
       </c>
       <c r="F38" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="G38" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="J38" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K38" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M38">
         <v>127</v>
@@ -2567,37 +2564,37 @@
       <c r="N38">
         <v>81</v>
       </c>
-      <c r="P38" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="R38" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E39" t="s">
-        <v>130</v>
+        <v>94</v>
+      </c>
+      <c r="E39">
+        <v>40</v>
       </c>
       <c r="F39" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J39" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K39" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L39" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M39">
         <v>116</v>
@@ -2605,37 +2602,37 @@
       <c r="N39">
         <v>80</v>
       </c>
-      <c r="P39" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="R39" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" t="s">
-        <v>131</v>
+        <v>94</v>
+      </c>
+      <c r="E40">
+        <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K40" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M40">
         <v>133</v>
@@ -2643,40 +2640,40 @@
       <c r="N40">
         <v>76</v>
       </c>
-      <c r="P40" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="R40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
-      </c>
-      <c r="E41" t="s">
-        <v>132</v>
+        <v>94</v>
+      </c>
+      <c r="E41">
+        <v>42</v>
       </c>
       <c r="F41" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="G41" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="H41">
         <v>4291035954</v>
       </c>
       <c r="J41" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="K41" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="M41">
         <v>129</v>
@@ -2684,8 +2681,8 @@
       <c r="N41">
         <v>79</v>
       </c>
-      <c r="P41" t="s">
-        <v>178</v>
+      <c r="R41" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
